--- a/SGC-CKN/Excel/d07cf31f-6954-405c-b5a2-e909e70e054e_Cọc_khoan_nhồi_P11-127_D800_14-04-2026.xlsx
+++ b/SGC-CKN/Excel/d07cf31f-6954-405c-b5a2-e909e70e054e_Cọc_khoan_nhồi_P11-127_D800_14-04-2026.xlsx
@@ -53,13 +53,13 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>08:30 14/04/2026</t>
+    <t>08:30 01/04/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>14:10 14/04/2026</t>
+    <t>14:10 01/04/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -99,11 +99,11 @@
   </si>
   <si>
     <t xml:space="preserve">08:30
-14/04/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">09:00
-14/04/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t/>
@@ -116,7 +116,7 @@
   </si>
   <si>
     <t xml:space="preserve">09:30
-14/04/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>3</t>
@@ -126,7 +126,7 @@
   </si>
   <si>
     <t xml:space="preserve">10:00
-14/04/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>4</t>
@@ -136,7 +136,7 @@
   </si>
   <si>
     <t xml:space="preserve">10:30
-14/04/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>5</t>
@@ -146,7 +146,7 @@
   </si>
   <si>
     <t xml:space="preserve">10:45
-14/04/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>6</t>
@@ -156,7 +156,7 @@
   </si>
   <si>
     <t xml:space="preserve">11:00
-14/04/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>7</t>
@@ -166,7 +166,7 @@
   </si>
   <si>
     <t xml:space="preserve">11:22
-14/04/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>8</t>
@@ -176,7 +176,7 @@
   </si>
   <si>
     <t xml:space="preserve">14:10
-14/04/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>

--- a/SGC-CKN/Excel/d07cf31f-6954-405c-b5a2-e909e70e054e_Cọc_khoan_nhồi_P11-127_D800_14-04-2026.xlsx
+++ b/SGC-CKN/Excel/d07cf31f-6954-405c-b5a2-e909e70e054e_Cọc_khoan_nhồi_P11-127_D800_14-04-2026.xlsx
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Sét pha, xám nâu, TT dẻo mềm</t>
+    <t>Sét pha, xám xanh, xám đen, xám nâu, xám ghi, TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">08:30
@@ -112,7 +112,7 @@
     <t>2</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">09:30
@@ -122,7 +122,7 @@
     <t>3</t>
   </si>
   <si>
-    <t>Sét - đôi chỗ kẹp cát pha, lẫn dăm sạn TT dẻo mềm</t>
+    <t>Sét, đôi chỗ kẹp cát pha, lẫn dăm sạn, TT dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">10:00
@@ -132,7 +132,7 @@
     <t>4</t>
   </si>
   <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT dẻo cứng</t>
+    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">10:30
@@ -142,7 +142,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Sét pha, xám xanh, xám ghi, TT dẻo mềm lẫn hữu cơ, kẹp cát</t>
+    <t>Sét pha - cát pha màu xám xanh, xám ghi, lẫn hữu cơ màu xám đen, trạng thái dẻo mềm</t>
   </si>
   <si>
     <t xml:space="preserve">10:45
@@ -152,7 +152,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát pha, xám vàng, xám ghi TT dẻo</t>
+    <t>Cát pha, xám ghi, xám nâu, xám vàng, TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">11:00
@@ -162,7 +162,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Cát thô vừa, KC chặt vừa lẫn sỏi sạn, có chỗ là hạt cát nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">11:22
@@ -172,7 +172,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">14:10
